--- a/Result/profitability/2460.xlsx
+++ b/Result/profitability/2460.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.41375</v>
+        <v>-0.35375</v>
       </c>
       <c r="N2" t="n">
-        <v>4.88375</v>
+        <v>5.212499999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.21375</v>
+        <v>-0.115</v>
       </c>
       <c r="N3" t="n">
-        <v>7.074999999999999</v>
+        <v>8.2925</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03499999999999998</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>9.848750000000001</v>
+        <v>10.8075</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005000000000000025</v>
+        <v>0.1</v>
       </c>
       <c r="N5" t="n">
-        <v>9.9825</v>
+        <v>11.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09875000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>12.31</v>
+        <v>14.72875</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0.46125</v>
       </c>
       <c r="N7" t="n">
-        <v>17.0775</v>
+        <v>17.82625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0.52625</v>
+        <v>0.53125</v>
       </c>
       <c r="N8" t="n">
-        <v>19.73625</v>
+        <v>19.54125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0.61875</v>
+        <v>0.6187499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>21.535</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1264</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1139</v>
+      </c>
+      <c r="E75" t="n">
+        <v>125</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>34</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>37</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4637500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3636363636363635</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.136482939632546</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.245901639344262</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>6.421052631578946</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
